--- a/Risk2SQL/data/GraphResult.xlsx
+++ b/Risk2SQL/data/GraphResult.xlsx
@@ -142,7 +142,7 @@
     <t>表：PRPS</t>
   </si>
   <si>
-    <t>WBS外码POSID、描述POST1、层级STUFE（为1或2）、类型PRART、投运日期USR08、对象号OBJNR、WBS内码PSPNR</t>
+    <t>WBS外码POSID、描述POST1、层级STUFE、类型PRART、投运日期USR08、对象号OBJNR、WBS内码PSPNR</t>
   </si>
   <si>
     <t>提供单体工程号、投运日期、项目WBS明细清单</t>
